--- a/test_data/WTA Treaties Menu/WTA Treaties Menu_Test_Cases.xlsx
+++ b/test_data/WTA Treaties Menu/WTA Treaties Menu_Test_Cases.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Full DTA' navigated to https://regplus.kaz.com.bd/wta/FullDta.</t>
+          <t>Clicking 'Full DTA' navigated to https://regplusrc.reganalytics.com/wta/FullDta.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'PE Clause' navigated to https://regplus.kaz.com.bd/wta/PEClauses.</t>
+          <t>Clicking 'PE Clause' navigated to https://regplusrc.reganalytics.com/wta/PEClauses.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Other Articles' navigated to https://regplus.kaz.com.bd/wta/OtherArticles.</t>
+          <t>Clicking 'Other Articles' navigated to https://regplusrc.reganalytics.com/wta/OtherArticles.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'WHT Rates' navigated to https://regplus.kaz.com.bd/wta/WHTRates.</t>
+          <t>Clicking 'WHT Rates' navigated to https://regplusrc.reganalytics.com/wta/WHTRates.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'MLI Data' navigated to https://regplus.kaz.com.bd/wta/MLIData?sort=jurisdiction%3Aasc.</t>
+          <t>Clicking 'MLI Data' navigated to https://regplusrc.reganalytics.com/wta/MLIData?sort=jurisdiction%3Aasc.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">

--- a/test_data/WTA Treaties Menu/WTA Treaties Menu_Test_Cases.xlsx
+++ b/test_data/WTA Treaties Menu/WTA Treaties Menu_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -568,306 +568,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TreatiesMenu_02_FullDTA</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>WTA Treaties Menu</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Treaties &gt; Full DTA navigates to its page</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Full DTA' in the Treaties dropdown must navigate to /wta/FullDta.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Menu item: Full DTA</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Open the Treaties dropdown
-3. Click 'Full DTA'
-4. Verify the URL contains /wta/FullDta</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Full DTA' in the Treaties dropdown must navigate to /wta/FullDta.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Full DTA' navigated to https://regplusrc.reganalytics.com/wta/FullDta.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] URL contains /wta/FullDta</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TreatiesMenu_02_PEClause</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>WTA Treaties Menu</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Treaties &gt; PE Clause navigates to its page</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'PE Clause' in the Treaties dropdown must navigate to /wta/PEClauses.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Menu item: PE Clause</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Open the Treaties dropdown
-3. Click 'PE Clause'
-4. Verify the URL contains /wta/PEClauses</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'PE Clause' in the Treaties dropdown must navigate to /wta/PEClauses.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'PE Clause' navigated to https://regplusrc.reganalytics.com/wta/PEClauses.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] URL contains /wta/PEClauses</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TreatiesMenu_02_OtherArticles</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>WTA Treaties Menu</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Treaties &gt; Other Articles navigates to its page</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Other Articles' in the Treaties dropdown must navigate to /wta/OtherArticles.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Menu item: Other Articles</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Open the Treaties dropdown
-3. Click 'Other Articles'
-4. Verify the URL contains /wta/OtherArticles</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Other Articles' in the Treaties dropdown must navigate to /wta/OtherArticles.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Other Articles' navigated to https://regplusrc.reganalytics.com/wta/OtherArticles.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] URL contains /wta/OtherArticles</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TreatiesMenu_02_WHTRates</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>WTA Treaties Menu</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Treaties &gt; WHT Rates navigates to its page</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'WHT Rates' in the Treaties dropdown must navigate to /wta/WHTRates.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Menu item: WHT Rates</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Open the Treaties dropdown
-3. Click 'WHT Rates'
-4. Verify the URL contains /wta/WHTRates</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'WHT Rates' in the Treaties dropdown must navigate to /wta/WHTRates.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'WHT Rates' navigated to https://regplusrc.reganalytics.com/wta/WHTRates.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] URL contains /wta/WHTRates</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TreatiesMenu_02_MLIData</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>WTA Treaties Menu</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Treaties &gt; MLI Data navigates to its page</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'MLI Data' in the Treaties dropdown must navigate to /wta/MLIData.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Menu item: MLI Data</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Open the Treaties dropdown
-3. Click 'MLI Data'
-4. Verify the URL contains /wta/MLIData</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'MLI Data' in the Treaties dropdown must navigate to /wta/MLIData.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'MLI Data' navigated to https://regplusrc.reganalytics.com/wta/MLIData?sort=jurisdiction%3Aasc.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] URL contains /wta/MLIData</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
